--- a/Excel/MapModeConfig.xlsx
+++ b/Excel/MapModeConfig.xlsx
@@ -1209,7 +1209,7 @@
         <v>1.6</v>
       </c>
       <c r="I6" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J6" s="1">
         <v>5</v>
